--- a/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_64917_completo.xlsx
+++ b/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_64917_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4e521862fb2e417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4c511bea17c44d68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.3355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.1473</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.6172</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.6553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.8450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.3261</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.6047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.6917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.5457</x:v>
+        <x:v>    104.2292</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.4267</x:v>
+        <x:v>    121.2807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    115.2538</x:v>
+        <x:v>    126.8421</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_64917_completo.xlsx
+++ b/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_64917_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4c511bea17c44d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R00b450f9dd3440b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.4428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.2335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.4901</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.6729</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.0641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.9770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.3068</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.9311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     95.1623</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.4073</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0591</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    130.8081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    128.5597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.2118</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.8088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8084</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.7613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.5540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    120.5283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.6770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.7182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.1439</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.1042</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.4027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.1909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.1077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.7048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.3329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.7108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.8214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.7920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.7139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.6776</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.5625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.8419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.9645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.4554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.2223</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.1691</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.3436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8371</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.8682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.8190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.5189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5079</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.3355</x:v>
+        <x:v>     84.8063</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2367</x:v>
+        <x:v>     88.9760</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.1473</x:v>
+        <x:v>     88.8993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.6172</x:v>
+        <x:v>     88.5898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.6553</x:v>
+        <x:v>     89.5945</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.8450</x:v>
+        <x:v>     92.9189</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3261</x:v>
+        <x:v>     94.2342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.6047</x:v>
+        <x:v>     90.1356</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.6917</x:v>
+        <x:v>     97.9489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.2292</x:v>
+        <x:v>    117.8072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.2807</x:v>
+        <x:v>    134.3119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    126.8421</x:v>
+        <x:v>    139.6995</x:v>
       </x:c>
     </x:row>
     <x:row>
